--- a/勤怠管理表_6人.xlsx
+++ b/勤怠管理表_6人.xlsx
@@ -12,7 +12,7 @@
     <sheet name="集計" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'勤怠管理表'!$A$5:$AE$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'勤怠管理表'!$A$5:$AH$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -975,13 +975,13 @@
       <c r="AH11" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AE11"/>
+  <autoFilter ref="A5:AH11"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AE1"/>
+    <mergeCell ref="A1:AH1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:AE11">
+  <conditionalFormatting sqref="D6:AH11">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(WEEKDAY(D$5,2)&gt;5,COUNTIF(祝日一覧!$A$2:$A$1000,D$5)&gt;0)</formula>
+      <formula>OR(WEEKDAY(D$5,2)&gt;5,COUNTIF('祝日一覧'!$A$2:$A$1000,D$5)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
